--- a/Data/MTR/MTR_DISTRICT.xlsx
+++ b/Data/MTR/MTR_DISTRICT.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\comp3522\Project\comp3522\data\MTR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\comp3522\Project\comp3522\Data\MTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCC3638-C8B6-47DA-9C22-8FAEECD25412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B038FB-2BC1-478B-B36A-A22A464CD79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$119</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="125">
   <si>
     <t>東區</t>
   </si>
@@ -101,6 +104,313 @@
   </si>
   <si>
     <t>Chinese_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>Sequence</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>博覽館</t>
+  </si>
+  <si>
+    <t>機場</t>
+  </si>
+  <si>
+    <t>青衣</t>
+  </si>
+  <si>
+    <t>九龍</t>
+  </si>
+  <si>
+    <t>香港</t>
+  </si>
+  <si>
+    <t>DRL</t>
+  </si>
+  <si>
+    <t>欣澳</t>
+  </si>
+  <si>
+    <t>迪士尼</t>
+  </si>
+  <si>
+    <t>EAL</t>
+  </si>
+  <si>
+    <t>羅湖</t>
+  </si>
+  <si>
+    <t>上水</t>
+  </si>
+  <si>
+    <t>粉嶺</t>
+  </si>
+  <si>
+    <t>太和</t>
+  </si>
+  <si>
+    <t>大埔墟</t>
+  </si>
+  <si>
+    <t>大學</t>
+  </si>
+  <si>
+    <t>火炭</t>
+  </si>
+  <si>
+    <t>沙田</t>
+  </si>
+  <si>
+    <t>大圍</t>
+  </si>
+  <si>
+    <t>九龍塘</t>
+  </si>
+  <si>
+    <t>旺角東</t>
+  </si>
+  <si>
+    <t>紅磡</t>
+  </si>
+  <si>
+    <t>會展</t>
+  </si>
+  <si>
+    <t>KTL</t>
+  </si>
+  <si>
+    <t>調景嶺</t>
+  </si>
+  <si>
+    <t>油塘</t>
+  </si>
+  <si>
+    <t>藍田</t>
+  </si>
+  <si>
+    <t>觀塘</t>
+  </si>
+  <si>
+    <t>牛頭角</t>
+  </si>
+  <si>
+    <t>九龍灣</t>
+  </si>
+  <si>
+    <t>彩虹</t>
+  </si>
+  <si>
+    <t>鑽石山</t>
+  </si>
+  <si>
+    <t>黃大仙</t>
+  </si>
+  <si>
+    <t>樂富</t>
+  </si>
+  <si>
+    <t>石硤尾</t>
+  </si>
+  <si>
+    <t>太子</t>
+  </si>
+  <si>
+    <t>旺角</t>
+  </si>
+  <si>
+    <t>油麻地</t>
+  </si>
+  <si>
+    <t>何文田</t>
+  </si>
+  <si>
+    <t>黃埔</t>
+  </si>
+  <si>
+    <t>SIL</t>
+  </si>
+  <si>
+    <t>海怡半島</t>
+  </si>
+  <si>
+    <t>利東</t>
+  </si>
+  <si>
+    <t>黃竹坑</t>
+  </si>
+  <si>
+    <t>海洋公園</t>
+  </si>
+  <si>
+    <t>TCL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>東涌</t>
+  </si>
+  <si>
+    <t>TCL</t>
+  </si>
+  <si>
+    <t>茘景</t>
+  </si>
+  <si>
+    <t>南昌</t>
+  </si>
+  <si>
+    <t>奧運</t>
+  </si>
+  <si>
+    <t>TKL</t>
+  </si>
+  <si>
+    <t>寶琳</t>
+  </si>
+  <si>
+    <t>坑口</t>
+  </si>
+  <si>
+    <t>將軍澳</t>
+  </si>
+  <si>
+    <t>TML</t>
+  </si>
+  <si>
+    <t>屯門</t>
+  </si>
+  <si>
+    <t>兆康</t>
+  </si>
+  <si>
+    <t>天水圍</t>
+  </si>
+  <si>
+    <t>朗屏</t>
+  </si>
+  <si>
+    <t>元朗</t>
+  </si>
+  <si>
+    <t>錦上路</t>
+  </si>
+  <si>
+    <t>荃灣西</t>
+  </si>
+  <si>
+    <t>美孚</t>
+  </si>
+  <si>
+    <t>柯士甸</t>
+  </si>
+  <si>
+    <t>尖東</t>
+  </si>
+  <si>
+    <t>土瓜灣</t>
+  </si>
+  <si>
+    <t>宋皇臺</t>
+  </si>
+  <si>
+    <t>啟德</t>
+  </si>
+  <si>
+    <t>顯徑</t>
+  </si>
+  <si>
+    <t>車公廟</t>
+  </si>
+  <si>
+    <t>沙田圍</t>
+  </si>
+  <si>
+    <t>第一城</t>
+  </si>
+  <si>
+    <t>石門</t>
+  </si>
+  <si>
+    <t>大水坑</t>
+  </si>
+  <si>
+    <t>恆安</t>
+  </si>
+  <si>
+    <t>馬鞍山</t>
+  </si>
+  <si>
+    <t>烏溪沙</t>
+  </si>
+  <si>
+    <t>TWL</t>
+  </si>
+  <si>
+    <t>荃灣</t>
+  </si>
+  <si>
+    <t>大窩口</t>
+  </si>
+  <si>
+    <t>葵興</t>
+  </si>
+  <si>
+    <t>葵芳</t>
+  </si>
+  <si>
+    <t>茘枝角</t>
+  </si>
+  <si>
+    <t>長沙灣</t>
+  </si>
+  <si>
+    <t>深水埗</t>
+  </si>
+  <si>
+    <t>佐敦</t>
+  </si>
+  <si>
+    <t>尖沙咀</t>
+  </si>
+  <si>
+    <t>南區</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>離島</t>
+  </si>
+  <si>
+    <t>油尖旺</t>
+  </si>
+  <si>
+    <t>九龍城</t>
+  </si>
+  <si>
+    <t>葵青</t>
+  </si>
+  <si>
+    <t>北區</t>
+  </si>
+  <si>
+    <t>大埔</t>
+  </si>
+  <si>
+    <t>九龍城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西貢</t>
+  </si>
+  <si>
+    <t>中西區</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -108,7 +418,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +430,13 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -432,14 +749,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F119"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="2" width="23.875" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -447,251 +765,2384 @@
         <v>21</v>
       </c>
       <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="D2" s="1">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="B3" s="1">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="1">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="1">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="1">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="1">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="1">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="1">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="1">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="1">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="1">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="1">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="1">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="1">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="1">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="1">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="1">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="1">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="1">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="1">
+        <v>10</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="1">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="1">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="1">
+        <v>11</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="1">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="1">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="1">
+        <v>13</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="1">
+        <v>6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="1">
+        <v>14</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="1">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="1">
+        <v>15</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="1">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="1">
+        <v>16</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="1">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="1">
+        <v>16</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="1">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="1">
+        <v>17</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="1">
+        <v>9</v>
+      </c>
+      <c r="E27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="1">
+        <v>18</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="1">
+        <v>8</v>
+      </c>
+      <c r="E28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="1">
+        <v>19</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="1">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="1">
+        <v>20</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="1">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="1">
+        <v>20</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="1">
+        <v>6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="1">
+        <v>21</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="1">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>119</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="1">
+        <v>21</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="1">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>119</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" s="1">
+        <v>22</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="1">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="1">
+        <v>23</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="1">
+        <v>24</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="1">
+        <v>25</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>106</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="1">
+        <v>26</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="1">
+        <v>14</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="1">
+        <v>27</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1">
+        <v>11</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="1">
+        <v>28</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="1">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="1">
+        <v>29</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="1">
+        <v>9</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1">
+        <v>30</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="1">
+        <v>8</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="1">
+        <v>31</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="1">
+        <v>7</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="1">
+        <v>31</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="1">
+        <v>7</v>
+      </c>
+      <c r="E44" t="s">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="1">
+        <v>32</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="1">
+        <v>6</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="1">
+        <v>32</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="1">
+        <v>6</v>
+      </c>
+      <c r="E46" t="s">
+        <v>0</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="1">
+        <v>33</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="1">
+        <v>5</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="1">
+        <v>34</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="1">
+        <v>4</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="1">
         <v>35</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F49" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1">
+        <v>36</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="1">
+        <v>37</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="1">
+        <v>38</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" s="1">
+        <v>3</v>
+      </c>
+      <c r="E52" t="s">
+        <v>54</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="1">
+        <v>39</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="1">
+        <v>8</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" s="1">
+        <v>40</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="E54" t="s">
+        <v>117</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B55" s="1">
+        <v>41</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="1">
+        <v>6</v>
+      </c>
+      <c r="E55" t="s">
+        <v>117</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" s="1">
+        <v>42</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" s="1">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>119</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" s="1">
+        <v>43</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1</v>
+      </c>
+      <c r="E57" t="s">
+        <v>116</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" s="1">
+        <v>44</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="1">
+        <v>5</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" s="1">
+        <v>45</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="E59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60" s="1">
+        <v>3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>119</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" s="1">
+        <v>47</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="1">
+        <v>2</v>
+      </c>
+      <c r="E61" t="s">
+        <v>116</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B62" s="1">
+        <v>48</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" s="1">
+        <v>2</v>
+      </c>
+      <c r="E62" t="s">
+        <v>54</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B63" s="1">
+        <v>48</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63" s="1">
+        <v>5</v>
+      </c>
+      <c r="E63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B64" s="1">
+        <v>49</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" s="1">
+        <v>49</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D65" s="1">
+        <v>4</v>
+      </c>
+      <c r="E65" t="s">
+        <v>123</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B66" s="1">
+        <v>50</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="1">
+        <v>3</v>
+      </c>
+      <c r="E66" t="s">
+        <v>123</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B67" s="1">
+        <v>51</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" s="1">
+        <v>2</v>
+      </c>
+      <c r="E67" t="s">
+        <v>123</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68" s="1">
+        <v>52</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
+        <v>123</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="1">
+        <v>53</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" s="1">
+        <v>5</v>
+      </c>
+      <c r="E69" t="s">
+        <v>112</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B70" s="1">
+        <v>53</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D70" s="1">
+        <v>9</v>
+      </c>
+      <c r="E70" t="s">
+        <v>112</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B71" s="1">
+        <v>54</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
+        <v>116</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="1">
+        <v>54</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="1">
+        <v>2</v>
+      </c>
+      <c r="E72" t="s">
+        <v>116</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B73" s="1">
+        <v>55</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D73" s="1">
+        <v>2</v>
+      </c>
+      <c r="E73" t="s">
+        <v>116</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B74" s="1">
+        <v>56</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="1">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>116</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B75" s="1">
+        <v>64</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" s="1">
+        <v>12</v>
+      </c>
+      <c r="E75" t="s">
+        <v>118</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1">
+        <v>64</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D76" s="1">
+        <v>12</v>
+      </c>
+      <c r="E76" t="s">
+        <v>118</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B77" s="1">
+        <v>65</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D77" s="1">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>117</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B78" s="1">
+        <v>67</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D78" s="1">
+        <v>9</v>
+      </c>
+      <c r="E78" t="s">
+        <v>44</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79" s="1">
+        <v>67</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" s="1">
+        <v>19</v>
+      </c>
+      <c r="E79" t="s">
+        <v>44</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B80" s="1">
+        <v>68</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="E80" t="s">
+        <v>44</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B81" s="1">
+        <v>69</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D81" s="1">
+        <v>7</v>
+      </c>
+      <c r="E81" t="s">
+        <v>44</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B82" s="1">
+        <v>71</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D82" s="1">
+        <v>6</v>
+      </c>
+      <c r="E82" t="s">
+        <v>44</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B83" s="1">
+        <v>72</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D83" s="1">
+        <v>5</v>
+      </c>
+      <c r="E83" t="s">
+        <v>121</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B84" s="1">
+        <v>73</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D84" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="1">
-        <v>33</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="E84" t="s">
+        <v>120</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B85" s="1">
+        <v>74</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D85" s="1">
+        <v>3</v>
+      </c>
+      <c r="E85" t="s">
+        <v>120</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B86" s="1">
+        <v>75</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D86" s="1">
+        <v>2</v>
+      </c>
+      <c r="E86" t="s">
+        <v>120</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B87" s="1">
+        <v>76</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D87" s="1">
+        <v>1</v>
+      </c>
+      <c r="E87" t="s">
+        <v>120</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B88" s="1">
+        <v>80</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D88" s="1">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s">
+        <v>117</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="1">
-        <v>32</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="B89" s="1">
+        <v>81</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="1">
+        <v>15</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" s="1">
+        <v>82</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="1">
+        <v>16</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" s="1">
+        <v>83</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D91" s="1">
+        <v>17</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B92" s="1">
+        <v>84</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D92" s="1">
+        <v>16</v>
+      </c>
+      <c r="E92" t="s">
+        <v>118</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B93" s="1">
+        <v>84</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D93" s="1">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>118</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B94" s="1">
+        <v>85</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D94" s="1">
+        <v>17</v>
+      </c>
+      <c r="E94" t="s">
+        <v>118</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B95" s="1">
+        <v>86</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D95" s="1">
+        <v>4</v>
+      </c>
+      <c r="E95" t="s">
+        <v>115</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B96" s="1">
+        <v>87</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D96" s="1">
+        <v>3</v>
+      </c>
+      <c r="E96" t="s">
+        <v>115</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B97" s="1">
+        <v>88</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D97" s="1">
+        <v>2</v>
+      </c>
+      <c r="E97" t="s">
+        <v>115</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B98" s="1">
+        <v>89</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" s="1">
+        <v>1</v>
+      </c>
+      <c r="E98" t="s">
+        <v>115</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B99" s="1">
+        <v>90</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D99" s="1">
+        <v>18</v>
+      </c>
+      <c r="E99" t="s">
+        <v>44</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B100" s="1">
+        <v>91</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D100" s="1">
+        <v>16</v>
+      </c>
+      <c r="E100" t="s">
+        <v>118</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B101" s="1">
+        <v>92</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D101" s="1">
+        <v>15</v>
+      </c>
+      <c r="E101" t="s">
+        <v>118</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B102" s="1">
+        <v>93</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D102" s="1">
+        <v>14</v>
+      </c>
+      <c r="E102" t="s">
+        <v>118</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B103" s="1">
+        <v>94</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D103" s="1">
+        <v>13</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B104" s="1">
+        <v>96</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D104" s="1">
+        <v>20</v>
+      </c>
+      <c r="E104" t="s">
+        <v>44</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B105" s="1">
+        <v>97</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D105" s="1">
+        <v>21</v>
+      </c>
+      <c r="E105" t="s">
+        <v>44</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B106" s="1">
+        <v>98</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D106" s="1">
+        <v>22</v>
+      </c>
+      <c r="E106" t="s">
+        <v>44</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B107" s="1">
+        <v>99</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D107" s="1">
+        <v>23</v>
+      </c>
+      <c r="E107" t="s">
+        <v>44</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B108" s="1">
+        <v>100</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D108" s="1">
+        <v>24</v>
+      </c>
+      <c r="E108" t="s">
+        <v>44</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B109" s="1">
+        <v>101</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D109" s="1">
+        <v>25</v>
+      </c>
+      <c r="E109" t="s">
+        <v>44</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B110" s="1">
+        <v>102</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D110" s="1">
+        <v>26</v>
+      </c>
+      <c r="E110" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B111" s="1">
+        <v>103</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D111" s="1">
+        <v>27</v>
+      </c>
+      <c r="E111" t="s">
+        <v>44</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B112" s="1">
+        <v>111</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D112" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="E112" t="s">
+        <v>117</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B113" s="1">
+        <v>114</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D113" s="1">
+        <v>7</v>
+      </c>
+      <c r="E113" t="s">
+        <v>106</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B114" s="1">
+        <v>115</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D114" s="1">
+        <v>6</v>
+      </c>
+      <c r="E114" t="s">
+        <v>87</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B115" s="1">
+        <v>116</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D115" s="1">
+        <v>5</v>
+      </c>
+      <c r="E115" t="s">
+        <v>87</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B116" s="1">
+        <v>117</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D116" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="1">
-        <v>31</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1">
-        <v>30</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1">
-        <v>29</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="E116" t="s">
+        <v>87</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B117" s="1">
+        <v>118</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D117" s="1">
+        <v>3</v>
+      </c>
+      <c r="E117" t="s">
+        <v>87</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B118" s="1">
+        <v>119</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D118" s="1">
+        <v>2</v>
+      </c>
+      <c r="E118" t="s">
+        <v>83</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B119" s="1">
+        <v>120</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D119" s="1">
         <v>1</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1">
-        <v>28</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="1">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="1">
-        <v>26</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="1">
-        <v>81</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="1">
-        <v>82</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="1">
+      <c r="E119" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>20</v>
+      <c r="F119" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F119" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F119">
+      <sortCondition ref="B1:B119"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
